--- a/daily_matches/job_matches_2026-06-19.xlsx
+++ b/daily_matches/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>ML Engineer ((GCP) – Finance Data &amp; AI Platform)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BizTech Fusion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka</t>
+          <t>Machine Learning Engineer, RAG, Copilot, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdecfd54adac1039</t>
+          <t>https://www.indeed.com/viewjob?jk=08ee595f70e46b33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,137 +531,137 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e4efb35b5bbb3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b09c16289d91a9c2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55aa01c630cde774</t>
+          <t>https://www.indeed.com/viewjob?jk=36c5a207a5141493</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9da9b6e57e35c1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=75337eae4d7f1ca4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245d5ee5ca6d437d</t>
+          <t>https://www.indeed.com/viewjob?jk=3778a847e69710fd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP /Python Data Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45beb918f8f1155</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce419a88fc032ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, PyTorch, Kubernetes, AKS</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5cfad207530e51</t>
+          <t>https://www.indeed.com/viewjob?jk=2228b29878769f7c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6aedd388d2a4f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d37d79e2a41923a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88766da5ca4c88b2</t>
+          <t>https://www.indeed.com/viewjob?jk=58947e3b3990b58a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Cassandra, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6443a98a089e97ef</t>
+          <t>https://www.indeed.com/viewjob?jk=74d31ddfd51c98d4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, MongoDB, NoSQL, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917258667f378b86</t>
+          <t>https://www.indeed.com/viewjob?jk=be3fa46940f05bde</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Transformation Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Git, BigQuery, PostgreSQL, MySQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8b184cd3dd463b</t>
+          <t>https://www.indeed.com/viewjob?jk=96ba9f5e4d52822c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e64f1257f37d3c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c36b54a1aabffc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8620a8d9e5b7bb26</t>
+          <t>https://www.indeed.com/viewjob?jk=07707c89f2c2beaf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758024d3413e1ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2773697f2a464bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a6284ae17b4c16</t>
+          <t>https://www.indeed.com/viewjob?jk=aca527a7ca4ae8cc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fad4021729b5dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=0668436ba0d957fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Orchestration Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8059e1261ee80f3</t>
+          <t>https://www.indeed.com/viewjob?jk=56e75a9810e146b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Digital Harbor Foundation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a015d80c139029</t>
+          <t>https://www.indeed.com/viewjob?jk=8e376f34a2464492</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbb2d8b3133abc99</t>
+          <t>https://www.indeed.com/viewjob?jk=b599a8fb3b53dca2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Advatix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09387918f778af8f</t>
+          <t>https://www.indeed.com/viewjob?jk=0666b2ee03b1b4ed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT Tools Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938a5c9fe77e4d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=210574454b039b8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, Kafka, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91cf70a2cea675c</t>
+          <t>https://www.indeed.com/viewjob?jk=01334b7e21714bf3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, LightGBM, Kafka, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72aca63c194658fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5758da877fbc35e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Application Engineer (Analytics &amp; Data Platforms) - Forsyth - Remote</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Databricks, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8118869043e787</t>
+          <t>https://www.indeed.com/viewjob?jk=7b88cc808352c6ed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>.NET Full Stack Architect (AWS) (On Site)</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Kubernetes, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312de1d62e70ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=e98cca52bbe68424</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>.NET Full Stack Architect (AWS) (On Site)</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Kubernetes, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,1792 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a5da28b2100e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e0cd792417383</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist- RF/Acoustics Signal Processing</t>
+          <t>AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cutsforth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9920b9b0db4e2308</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94af0e0a513dab44</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9da85b011f3c9bb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f747e8cd9f65503</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e6716e1346a404f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f32c63274ea61adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed88553db5377339</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc602142c0dc423a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69d3c14f109508ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29431c61744eb526</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer II or III</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D39" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ab1bd8dcae6ad9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Glue, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c248fdc62311341</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>American Family Insurance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, NoSQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9add9193adcfdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, CI/CD, Databricks</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea91413547821117</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Developer - Application Development JAVA N 4B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3d7faea93986590</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Software Engineer – Agentic AI System</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca37df0652f06170</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer- Investment Research and Data</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f71b2d395389103</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sequoia Financial Group</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dublin, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Azure ML, Azure ML Studio, MLflow, Git, Databricks, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f9827b961c4b0e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sequoia Financial Group</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mayfield Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Azure ML, Azure ML Studio, MLflow, Git, Databricks, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bf5c69af39e96c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sequoia Financial Group</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Azure ML, Azure ML Studio, MLflow, Git, Databricks, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57bfcbe6e39a6f14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Docker, Jenkins, Git, Databricks, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cf3a91683e2fbee</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - AI Innovation Team</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BECU</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=893eebcde0f6a410</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mid Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sunwest Bank</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sandy, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3fc340c895d6105</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dbt Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Blue Cross of Idaho</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Meridian, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfe4cac7fc101255</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI/ML Research Engineer, LLM Post-Training &amp; Evaluation</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ridgefield Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82444c16429fabac</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software QA Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bhrigu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5be5bdbba98018f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Associate, Software Engineer, Applications</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=956dc941dad64afb</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6311a108ad80bb92</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33be6ad8554d742c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df821de8d132357f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2089837e6829217a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3ff5e782db450e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8f7ac845745180</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ad2851c92dff47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Engineering Enablement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ab9cff34d4c4cd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cretelligent</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Gold River, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f559b806c28f9c62</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Cloud - Native Application Engineer (Java / .NET)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6c6b81b37cfb8f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11adfd198420fc84</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Kafka, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3fccdbde5e44c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer, Fullstack and Developer Experience</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bea3e6c2fbbe5741</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1927b44823815f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Core BTS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc83ddd45a1d6c4</t>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Databricks, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48b5bf75af922dd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ac9681ff49c88cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, CI/CD, Jenkins, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=721d9652b5714e1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, CI/CD, Jenkins, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=202dce1cf6f1ad82</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aea3be9cd5ede06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Full Stack Application Engineer (Analytics &amp; Data Platforms) - Forsyth - Remote</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, Databricks, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=345e96897f9c03d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior ML Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=681cbd88417b3f77</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Analyst/Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf7722ed5af37806</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior AI Data Scientist (Generative AI &amp; Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hiring Group</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Kubernetes, PySpark, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a40d7b43ef148e77</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, LLaMA, FAISS, Pinecone, CI/CD, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4f405fe3d906b7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-19.xlsx
+++ b/daily_matches/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Product Software Engineer I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL</t>
+          <t>Data Scientist, RAG, Kinesis, Docker, Kubernetes, Terraform, Snowflake, Databricks, Kafka, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9251732e66580bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data + BI) — Healthcare</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Docker, CI/CD, Terraform, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,707 +531,217 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e342cff8300db11b</t>
+          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, AI &amp; Agentic Systems</t>
+          <t>Senior Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42af33fba010bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=a42ad39cb3a040ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Information Products Team</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, BigQuery, Docker, CI/CD, GitHub Actions, Git, BigQuery</t>
+          <t>S3, Glue, CI/CD, Git, PySpark, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4bf3a4fb736dcb</t>
+          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Data, AI/ML &amp; Analytics</t>
+          <t>Systems Engineer - Onsite in Dallas, TX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IT Services Consulting Solutions</t>
+          <t>United Surgical Partners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Databricks, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932f0e4ff1dd485b</t>
+          <t>https://www.indeed.com/viewjob?jk=c27c7200e635b4c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blackhawk Network</t>
+          <t>Hack The Box</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3ee41a8c52420bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a10d821306fc8600</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior Associate, Analytics Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Tudip Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, BigQuery, CI/CD, Git, Databricks, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6fe876bea05203</t>
+          <t>https://www.indeed.com/viewjob?jk=beae79787bce99c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Assoc. Spclst , Software Engineering</t>
+          <t>Senior Engineer, AI Applications Development</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b9269913a205bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Amgen</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Thousand Oaks, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, AKS, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d03bddfec1ac1f72</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DevFinOps Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84a584e2ae5c7382</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK, Python, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf6089fe1ed8784</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16827b9e1e789ec7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=580c050c08eb0a8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Science Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Databricks, Tableau, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b31f13d8496041</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Brentwood, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a583130162de58</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior ML Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NYU Langone Health</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac05e1ca0a3e98d</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Marketing Technologies Engineer (Analytics) — Growth &amp; Martech Engineering</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7f187cda3b16e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e235bc7e9c4f9ac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Associate - Enterprise Intelligence Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BigQuery, Git, Databricks, BigQuery, Tableau, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f738fb7e1c97b094</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Associate - AI Product Scientist, Decision Intelligence</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, MLflow, Databricks, Python, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2445057f8cfc8414</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Engineer 2 - Reston, VA - Freewheel</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Databricks, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dda6c323afa00a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Transformation Specialist</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Schneider Electric</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Franklin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6f2a06ce659c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d549817a93c2f400</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-19.xlsx
+++ b/daily_matches/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Product Software Engineer I</t>
+          <t>Senior Software Engineer - LSP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kinesis, Docker, Kubernetes, Terraform, Snowflake, Databricks, Kafka, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5d705afdfcef3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>DevOps &amp; Security Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>HSI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46e5e7f505da6aea</t>
+          <t>https://www.indeed.com/viewjob?jk=ca54d4b303fc15a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, PySpark, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Snowflake, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a42ad39cb3a040ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Information Products Team</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Dealer Tire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, Glue, CI/CD, Git, PySpark, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59625199b42cb5da</t>
+          <t>https://www.indeed.com/viewjob?jk=5fefc9455e2c65b5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Systems Engineer - Onsite in Dallas, TX</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Surgical Partners</t>
+          <t>Dealer Tire</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c27c7200e635b4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef27ab3dae795e9b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Financial Services - Senior - Data Scientist - EDGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hack The Box</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, AKS, CI/CD, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a10d821306fc8600</t>
+          <t>https://www.indeed.com/viewjob?jk=1abfcef94beb25c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tudip Technologies Pvt Ltd</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, Docker, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beae79787bce99c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d23f6276f13b3fd9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI Applications Development</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,21 +727,56 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Gemini, Docker, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d549817a93c2f400</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd85f775aa6c5dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Agentic AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Data Lake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e586a6fca9463dd9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-19.xlsx
+++ b/daily_matches/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - LSP</t>
+          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>S3, EC2, Athena, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d185ef3015154b1f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer II</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HSI</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca54d4b303fc15a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Consultant — System Integration &amp; MDM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>Triade Flevoland</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Snowflake, Power BI, SQL, R, Scala</t>
+          <t>Copilot, Glue, Terraform, Snowflake, Databricks, Kafka, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb77bd035c0b222</t>
+          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer (SMTS / LMTS) - MDM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dealer Tire</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fefc9455e2c65b5</t>
+          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Software Engineer, GenAI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dealer Tire</t>
+          <t>TRICENTIS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef27ab3dae795e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c33063e013846ceb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financial Services - Senior - Data Scientist - EDGE</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, AKS, CI/CD, Power BI, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abfcef94beb25c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hudson Manpower</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Docker, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d23f6276f13b3fd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Hudson Manpower</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Docker, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd85f775aa6c5dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Agentic AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EXL Service</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Data Lake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e586a6fca9463dd9</t>
+          <t>https://www.indeed.com/viewjob?jk=099e446b59d8c602</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-19.xlsx
+++ b/daily_matches/job_matches_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer - IN PERSON - WIXOM MI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Athena, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2db67e76b3a6ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=da3c07885d8b3693</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Intellisoft Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>RAG, BigQuery, Dataflow, Apache Airflow, Git, BigQuery, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6a3f2e51311a48</t>
+          <t>https://www.indeed.com/viewjob?jk=8c473d3620c861ac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Consultant — System Integration &amp; MDM</t>
+          <t>Senior Software Engineer - Bruin Platform Full Stack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Glue, Terraform, Snowflake, Databricks, Kafka, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d22f323af4989133</t>
+          <t>https://www.indeed.com/viewjob?jk=e6f34508146cf3d4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (SMTS / LMTS) - MDM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, Glue, Kinesis, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50844673569c1fb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c434dda73e4155</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, GenAI</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TRICENTIS</t>
+          <t>Mem0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>S3, EC2, FastAPI, Docker, Kubernetes, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c33063e013846ceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=099e446b59d8c602</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ab0104e01283dc</t>
         </is>
       </c>
     </row>
